--- a/Integration_Test_Cases_Final.xlsx
+++ b/Integration_Test_Cases_Final.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Project Portfolio" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Warehouse and Inventory" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Incident Management" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Reports Hub" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6072,4 +6073,1137 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:O30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Report Module</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Test requirement</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Verify executive, construction progress, BOQ limits, incidents, inventory movement, and procurement expense reporting workflows from the user's screen through saved results. Procedures use visible menus, tabs, date filters, drop-downs and tables only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Number of TCs</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Testing Round</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Round 1</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>COUNTIF($F$11:$F$30,B$5)</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>COUNTIF($F$11:$F$30,C$5)</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>COUNTIF($F$11:$F$30,D$5)</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>COUNTIF($F$11:$F$30,E$5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Round 2</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>COUNTIF($I$11:$I$30,B$5)</f>
+        <v/>
+      </c>
+      <c r="C7" s="3">
+        <f>COUNTIF($I$11:$I$30,C$5)</f>
+        <v/>
+      </c>
+      <c r="D7" s="3">
+        <f>COUNTIF($I$11:$I$30,D$5)</f>
+        <v/>
+      </c>
+      <c r="E7" s="3">
+        <f>COUNTIF($I$11:$I$30,E$5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Round 3</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>COUNTIF($L$11:$L$30,B$5)</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>COUNTIF($L$11:$L$30,C$5)</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>COUNTIF($L$11:$L$30,D$5)</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>COUNTIF($L$11:$L$30,E$5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Test Case Description</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Test Case Procedure</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Round 1</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Test date</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Round 2</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Test date</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>Round 3</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>Test date</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>UC-301 - View project executive dashboard (Overview)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="n"/>
+      <c r="N11" s="6" t="n"/>
+      <c r="O11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="65" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>TC-01</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>User views project executive overview metrics, phase progress breakdown and delayed task warnings</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>1. Open the BPG-CMS website in a browser.
+2. Log in with Technical Manager account.
+3. On left sidebar, click 'Trung tâm Báo cáo' menu.
+4. Select project 'Dự án Nhà phố BPG' from top project selector dropdown.
+5. Click tab 'Tổng quan'.
+6. Inspect stats cards (Total Tasks, Completed Tasks, In Progress Tasks, Delayed Tasks, At Risk Tasks, Over-BOQ Materials), phase breakdown table, and delayed tasks list.</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>1. Top stats cards render correct project metrics.
+2. Phase breakdown table shows Phase Name, Status, Total Tasks, Completed Tasks, and Progress (%).
+3. Delayed tasks list displays Task Name, Phase Name, End Date, Assignee Name, Progress, and Red/Yellow warning level indicators.</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>1. The BPG-CMS website is operational and can be accessed.
+2. Saved data can be loaded from DB successfully.
+3. 'Dự án Nhà phố BPG' has active tasks and phases.</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="9" t="n"/>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="n"/>
+      <c r="K12" s="9" t="n"/>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="n"/>
+      <c r="N12" s="9" t="n"/>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="65" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>TC-02</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Filter executive overview report by Global Date Range Filter</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>1. In 'Tổng quan' tab of Reports Hub, select 'Từ ngày': '01/08/2026' and 'Đến ngày': '31/08/2026' (or click preset button '30 ngày qua').
+2. Observe update of report metrics.</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>1. Report metrics, phase breakdown progress, and delayed task lists refresh displaying data filtered strictly within the selected date range.</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>1. The BPG-CMS website is operational and can be accessed.
+2. Project has task records across multiple date ranges.</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="9" t="n"/>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="9" t="n"/>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M13" s="9" t="n"/>
+      <c r="N13" s="9" t="n"/>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="65" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>TC-03</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Placeholder display when no project is selected</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>1. In Reports Hub, clear top project selection (select 'Chọn dự án...').</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>1. Report area displays placeholder prompt: 'Vui lòng chọn một dự án để xem báo cáo.'.</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>1. The BPG-CMS website is operational and can be accessed.</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="9" t="n"/>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n"/>
+      <c r="K14" s="9" t="n"/>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="n"/>
+      <c r="N14" s="9" t="n"/>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>UC-302 - View project construction progress report</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="n"/>
+      <c r="N15" s="6" t="n"/>
+      <c r="O15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="65" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>TC-01</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>User views construction progress task status breakdown per phase and phase acceptance records</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>1. Open Reports Hub, select project 'Dự án Nhà phố BPG'.
+2. Click tab 'Tiến độ Thi công'.
+3. Inspect top stats (Completed, In Progress, Assigned, New, Obsolete counts, Overall Progress %) and phase task sub-tables.
+4. Scroll to 'Lịch sử Nghiệm thu Giai đoạn' table.</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>1. Top stats render correct task counts and overall progress %.
+2. Each phase renders a dedicated section with start/end dates, progress bar %, and task detail table.
+3. Phase acceptance table lists Phase Name, Acceptance Date, Acceptor Name, and Cancellation status with cancellation reason if applicable.</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>1. The BPG-CMS website is operational and can be accessed.
+2. Saved data can be loaded from DB successfully.
+3. Project has phase acceptance records.</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="n"/>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="n"/>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M16" s="9" t="n"/>
+      <c r="N16" s="9" t="n"/>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="65" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>TC-02</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Obsolete tasks are excluded from active progress calculations but preserved in historical logs</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>1. Inspect top stats card 'Công việc đã hủy (Obsolete)' and task status column in 'Tiến độ Thi công' tab.</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>1. Obsolete tasks are listed with status tag 'Đã hủy' for historical audit.
+2. Progress percentage calculations exclude Obsolete tasks from total active task scope.</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>1. The BPG-CMS website is operational and can be accessed.
+2. Project has at least one Obsolete task.</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="9" t="n"/>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="9" t="n"/>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M17" s="9" t="n"/>
+      <c r="N17" s="9" t="n"/>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>UC-303 - View project BOQ vs Actual report</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
+      <c r="N18" s="6" t="n"/>
+      <c r="O18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="65" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>TC-01</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>User views material BOQ limit vs actual consumption comparison report</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>1. Open Reports Hub, select project 'Dự án Nhà phố BPG'.
+2. Click tab 'Định mức BOQ'.
+3. Inspect material analysis table.</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>1. Table displays Material Code, Name, Unit, BOQ Planned Limit, Actual Issues, Returns, Net Consumption, Remaining Stock, Pending POs, Total Expected Usage, Exceeded Amount, and Usage Ratio (%).
+2. Usage Ratio (%) is calculated as (Total Expected Usage / BOQ Limit) * 100.</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>1. The BPG-CMS website is operational and can be accessed.
+2. Saved data can be loaded from DB successfully.
+3. Project has BOQ limits and material issuances.</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="9" t="n"/>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="9" t="n"/>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="n"/>
+      <c r="N19" s="9" t="n"/>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="65" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>TC-02</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Red alert highlight on material items exceeding BOQ planned limits</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>1. Inspect rows for materials where Total Expected Usage &gt; BOQ Planned Limit (e.g. 'Xi măng PCB40').</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>1. Material row is highlighted in red alert background.
+2. Column 'Vượt định mức' displays 'Có' with calculated exceeded quantity.
+3. Exceeded Amount is calculated as Total Expected Usage - BOQ Limit.</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>1. The BPG-CMS website is operational and can be accessed.
+2. Project has material items exceeding BOQ planned limit.</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="9" t="n"/>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n"/>
+      <c r="K20" s="9" t="n"/>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M20" s="9" t="n"/>
+      <c r="N20" s="9" t="n"/>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>UC-304 - View project incident summary report</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n"/>
+      <c r="M21" s="6" t="n"/>
+      <c r="N21" s="6" t="n"/>
+      <c r="O21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="65" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>TC-01</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>User views incident summary stats and clean description log table</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>1. Open Reports Hub, select project 'Dự án Nhà phố BPG'.
+2. Click tab 'Sự cố &amp; Rework'.
+3. Inspect stats cards (Total Incidents, Open Incidents, Resolved Incidents, Rework Incidents) and incident summary table.</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>1. Stats cards display correct summary counts.
+2. Incident table displays Incident Code, Type (Construction/Inventory), Description narrative, Status, Reporter, Phase/Task, Estimated Damage/Delay, and linked Rework Task.
+3. Description column automatically parses out markdown date/time tags to render clean text narrative.</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>1. The BPG-CMS website is operational and can be accessed.
+2. Saved data can be loaded from DB successfully.
+3. Project has construction and inventory incidents.</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="9" t="n"/>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="9" t="n"/>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M22" s="9" t="n"/>
+      <c r="N22" s="9" t="n"/>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>UC-305 - View project inventory ledger report</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="n"/>
+      <c r="N23" s="6" t="n"/>
+      <c r="O23" s="6" t="n"/>
+    </row>
+    <row r="24" ht="65" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>TC-01</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>User views project virtual warehouse inventory ledger and stock movement audit log</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>1. Open Reports Hub, select project 'Dự án Nhà phố BPG'.
+2. Click tab 'Nhập xuất tồn'.
+3. Inspect stats cards, 'Tồn kho &amp; Luân chuyển' table, and 'Nhật ký Giao dịch Kho' table.</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>1. Table 1 displays Material Code, Name, Unit, Opening Balance, Period Receipts, Period Issuances, Period Returns, and Closing Balance.
+2. Table 2 displays Transaction Date, Material Code, Material Name, Reference Type (Allocation, Return, Incident adjustment, Transfer), Quantity Change (+/-), Balance After, and Operator Name.</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>1. The BPG-CMS website is operational and can be accessed.
+2. Saved data can be loaded from DB successfully.
+3. Project has inventory transactions.</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="9" t="n"/>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M24" s="9" t="n"/>
+      <c r="N24" s="9" t="n"/>
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="65" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>TC-02</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Filter inventory ledger by date range</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>1. Select date range '01/08/2026' to '15/08/2026' in top filter bar.</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>1. Opening balance is calculated prior to 01/08/2026.
+2. Receipts, issuances, returns and transaction logs filter strictly within 01/08/2026 - 15/08/2026.</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>1. The BPG-CMS website is operational and can be accessed.</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="9" t="n"/>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="9" t="n"/>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="n"/>
+      <c r="N25" s="9" t="n"/>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>UC-306 - View project procurement and cost report</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="6" t="n"/>
+      <c r="L26" s="6" t="n"/>
+      <c r="M26" s="6" t="n"/>
+      <c r="N26" s="6" t="n"/>
+      <c r="O26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="65" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>TC-01</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>User views procurement expenses consolidated report (Purchase Orders and Direct Purchases)</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>1. Open Reports Hub, select project 'Dự án Nhà phố BPG'.
+2. Click tab 'Mua sắm &amp; Chi phí'.
+3. Inspect stats cards (Total PO Cost, Total Direct Purchase Cost, Sum Total Expenses) and tables.</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>1. Sum Total Expenses card equals Total PO Cost + Total Direct Purchase Cost.
+2. Table 'Danh sách Đơn đặt hàng (PO)' lists PO Number, Status, Supplier, Total Amount, Order Date, and Delivery Date.
+3. Table 'Danh sách Mua hàng trực tiếp' lists Requester Name, Status, Total Amount, Invoice Image Attachment link, and Created Date.</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>1. The BPG-CMS website is operational and can be accessed.
+2. Saved data can be loaded from DB successfully.
+3. Project has approved POs and direct purchases.</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="9" t="n"/>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n"/>
+      <c r="K27" s="9" t="n"/>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M27" s="9" t="n"/>
+      <c r="N27" s="9" t="n"/>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>UC-307 - View portfolio dashboard (All projects)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
+      <c r="L28" s="6" t="n"/>
+      <c r="M28" s="6" t="n"/>
+      <c r="N28" s="6" t="n"/>
+      <c r="O28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="65" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>TC-01</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Management role views portfolio dashboard across all company projects</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>1. Log in with Technical Manager account.
+2. Open Reports Hub, select 'Tất cả dự án' from top project selector dropdown.
+3. Inspect Portfolio stats cards, project status distribution chart, and progress comparison list.</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>1. Stats cards render Total Projects, Average Progress (%), Active Projects, Paused Projects, and Completed Projects.
+2. Status distribution pie chart and project progress comparison bars display company-wide performance metrics.</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>1. The BPG-CMS website is operational and can be accessed.
+2. Technical Manager account is logged in.
+3. Multiple projects exist in system.</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="9" t="n"/>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n"/>
+      <c r="K29" s="9" t="n"/>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M29" s="9" t="n"/>
+      <c r="N29" s="9" t="n"/>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="65" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>TC-02</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Non-manager role is blocked from selecting 'Tất cả dự án' view</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>1. Log in with Site Engineer account.
+2. Open Reports Hub, inspect top project selector dropdown options.</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>1. Option 'Tất cả dự án' is hidden or disabled in dropdown.
+2. Site Engineer can only select individual projects assigned to them.</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>1. The BPG-CMS website is operational and can be accessed.
+2. Site Engineer account is logged in.</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="9" t="n"/>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="n"/>
+      <c r="K30" s="9" t="n"/>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M30" s="9" t="n"/>
+      <c r="N30" s="9" t="n"/>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B4:E4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>